--- a/public/assets/template/franchise-template.xlsx
+++ b/public/assets/template/franchise-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ndejo\Documents\GitHub\tokusatsu\public\assets\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D03BB9C-35F5-4D40-9645-E46BBEE86356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{530B09A3-3B36-4A44-AC9D-F3F2211F8039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{51F6D04B-38A7-4907-901E-8D2AF0D93E74}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Name</t>
   </si>
@@ -49,6 +49,15 @@
   </si>
   <si>
     <t>Garo</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Images</t>
+  </si>
+  <si>
+    <t>Data Franchise</t>
   </si>
 </sst>
 </file>
@@ -86,7 +95,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -109,16 +118,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -435,10 +456,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A86521A1-DC6B-4F40-AA0D-147BEF52CF9B}">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.85546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="3.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.85546875" style="1" customWidth="1"/>
@@ -446,32 +467,60 @@
     <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="C2" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
         <v>3</v>
       </c>
+      <c r="B5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
